--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -468,11 +468,11 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1525720252939207</v>
+        <v>-0.01142128659170394</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2849646041194856</v>
+        <v>0.1683187949836017</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.6529170519007764</v>
+        <v>-0.08164087871284276</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.9553871210878532</v>
+        <v>-0.1125292543534281</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1951963114869354</v>
+        <v>0.1512732119916019</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8916816257518412</v>
+        <v>-0.08525600137504522</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>63.50051310703153</v>
+        <v>29.18095634511499</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.4163967449175487</v>
+        <v>-0.2060724190208458</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2518272343622115</v>
+        <v>0.2832764451631418</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-2.157604619405249</v>
+        <v>-0.7595692512314294</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.708012139990607</v>
+        <v>-1.068411857650868</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.435676099107362</v>
+        <v>0.2550439882431181</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9852284807271444</v>
+        <v>-0.8375302819629658</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>61.65290316869333</v>
+        <v>46.73941252628944</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1734382578710221</v>
+        <v>-0.06460003330109809</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.215092277025857</v>
+        <v>0.2268064922875767</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.883870807403132</v>
+        <v>-0.2589505633952272</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-1.232596553816966</v>
+        <v>-0.3530230006739213</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2524289909828417</v>
+        <v>0.226434920972167</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.7127496380511019</v>
+        <v>-0.2966757782137046</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>67.89228053729101</v>
+        <v>65.72804942968233</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1408462657083676</v>
+        <v>0.06871418579155408</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2476283924502877</v>
+        <v>0.3495079701499129</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.5764672540175926</v>
+        <v>0.3283887413825879</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.8853739498695713</v>
+        <v>0.4918202426559175</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2426601745332559</v>
+        <v>0.2160077976876583</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.6025665189924627</v>
+        <v>0.331715071977272</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>73.03374339603677</v>
+        <v>71.87241721935013</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.001310210742859752</v>
+        <v>-0.1566129143811142</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2375171260664232</v>
+        <v>0.2546967256929211</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.05132804852679952</v>
+        <v>-0.6229718967220088</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.06732590120361229</v>
+        <v>-0.7938066148700005</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2048024937463754</v>
+        <v>0.3177181081798457</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.006634216511156782</v>
+        <v>-0.5096236661000501</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>74.30503548095454</v>
+        <v>78.55214192440542</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1321319277183728</v>
+        <v>0.5366990434171106</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.2951673446593391</v>
+        <v>0.3926197412381553</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8589606531083718</v>
+        <v>2.143324426391423</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.240918069600815</v>
+        <v>3.405291265713471</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2018446737306093</v>
+        <v>0.1583732007310199</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.250031565529076</v>
+        <v>7.445040271911074</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>61.40632842640726</v>
+        <v>54.16012923725231</v>
       </c>
     </row>
   </sheetData>
